--- a/AAII_Financials/Yearly/HBRIY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HBRIY_YR_FIN.xlsx
@@ -1152,7 +1152,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>301000</v>
+        <v>296000</v>
       </c>
       <c r="E20" s="3">
         <v>32000</v>
@@ -1194,7 +1194,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3648000</v>
+        <v>3653000</v>
       </c>
       <c r="E21" s="3">
         <v>2054000</v>
@@ -1236,7 +1236,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>244000</v>
+        <v>249000</v>
       </c>
       <c r="E22" s="3">
         <v>123000</v>
@@ -1656,7 +1656,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-301000</v>
+        <v>-296000</v>
       </c>
       <c r="E32" s="3">
         <v>-32000</v>
